--- a/Data/Variations.xlsx
+++ b/Data/Variations.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="574">
   <si>
     <t>flatten</t>
   </si>
@@ -1734,6 +1734,9 @@
   </si>
   <si>
     <t>crackle</t>
+  </si>
+  <si>
+    <t>smartshape</t>
   </si>
 </sst>
 </file>
@@ -3690,11 +3693,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="108275712"/>
-        <c:axId val="89839232"/>
+        <c:axId val="40138752"/>
+        <c:axId val="108909632"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="108275712"/>
+        <c:axId val="40138752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3703,7 +3706,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="89839232"/>
+        <c:crossAx val="108909632"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3711,7 +3714,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89839232"/>
+        <c:axId val="108909632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3722,7 +3725,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="108275712"/>
+        <c:crossAx val="40138752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4065,7 +4068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I314"/>
+  <dimension ref="A1:I298"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
@@ -4277,8 +4280,8 @@
       <c r="E14" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>420</v>
+      <c r="G14" s="3" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -4292,7 +4295,7 @@
         <v>110</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>567</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -4362,6 +4365,9 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="E22" s="4" t="s">
         <v>117</v>
       </c>
@@ -4370,8 +4376,8 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>13</v>
+      <c r="A23" s="2" t="s">
+        <v>393</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>118</v>
@@ -4381,8 +4387,8 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>393</v>
+      <c r="A24" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>119</v>
@@ -4392,32 +4398,32 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>51</v>
+      <c r="A25" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>239</v>
+      <c r="A26" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>52</v>
+      <c r="A27" s="2" t="s">
+        <v>233</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>233</v>
+      <c r="A28" s="3" t="s">
+        <v>246</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>123</v>
@@ -4425,7 +4431,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>246</v>
+        <v>304</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>124</v>
@@ -4433,7 +4439,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>125</v>
@@ -4441,7 +4447,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>126</v>
@@ -4449,7 +4455,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>127</v>
@@ -4457,23 +4463,23 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>280</v>
+        <v>53</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>53</v>
+      <c r="A34" s="5" t="s">
+        <v>270</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>270</v>
+      <c r="A35" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>130</v>
@@ -4481,15 +4487,15 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>256</v>
+      <c r="A37" s="2" t="s">
+        <v>235</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>132</v>
@@ -4497,15 +4503,15 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>234</v>
+      <c r="A39" s="3" t="s">
+        <v>377</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>134</v>
@@ -4513,7 +4519,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>135</v>
@@ -4521,7 +4527,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>376</v>
+        <v>54</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>136</v>
@@ -4529,7 +4535,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>54</v>
+        <v>379</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>137</v>
@@ -4537,7 +4543,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>138</v>
@@ -4545,23 +4551,23 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>378</v>
+        <v>55</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>55</v>
+      <c r="A45" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>56</v>
+      <c r="A46" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>141</v>
@@ -4569,20 +4575,23 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>197</v>
+        <v>94</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>247</v>
+      </c>
       <c r="E48" s="4" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>94</v>
+        <v>381</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>144</v>
@@ -4590,15 +4599,15 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>247</v>
+        <v>380</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>381</v>
+      <c r="A51" s="2" t="s">
+        <v>389</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>146</v>
@@ -4606,15 +4615,15 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>380</v>
+        <v>348</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>389</v>
+      <c r="A53" s="3" t="s">
+        <v>349</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>148</v>
@@ -4622,7 +4631,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>348</v>
+        <v>16</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>149</v>
@@ -4630,7 +4639,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>349</v>
+        <v>383</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>150</v>
@@ -4638,7 +4647,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>151</v>
@@ -4646,7 +4655,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>383</v>
+        <v>198</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>152</v>
@@ -4654,39 +4663,39 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>57</v>
+        <v>350</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>198</v>
+      <c r="A59" s="2" t="s">
+        <v>242</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>350</v>
+      <c r="A60" s="2" t="s">
+        <v>327</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>242</v>
+      <c r="A61" s="3" t="s">
+        <v>257</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>327</v>
+      <c r="A62" s="3" t="s">
+        <v>258</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>157</v>
@@ -4694,7 +4703,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>158</v>
@@ -4702,7 +4711,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>159</v>
@@ -4710,7 +4719,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>160</v>
@@ -4718,7 +4727,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>260</v>
+        <v>199</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>161</v>
@@ -4726,7 +4735,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>261</v>
+        <v>12</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>162</v>
@@ -4734,15 +4743,15 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>199</v>
+        <v>262</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>12</v>
+      <c r="A69" s="2" t="s">
+        <v>390</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>164</v>
@@ -4750,15 +4759,15 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
-        <v>390</v>
+      <c r="A71" s="3" t="s">
+        <v>264</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>166</v>
@@ -4766,7 +4775,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>263</v>
+        <v>382</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>167</v>
@@ -4774,7 +4783,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>168</v>
@@ -4782,7 +4791,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>382</v>
+        <v>58</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>169</v>
@@ -4790,7 +4799,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>265</v>
+        <v>59</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>170</v>
@@ -4798,7 +4807,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>58</v>
+        <v>424</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>171</v>
@@ -4806,7 +4815,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>172</v>
@@ -4814,7 +4823,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>424</v>
+        <v>299</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>173</v>
@@ -4822,7 +4831,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>20</v>
+        <v>367</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>174</v>
@@ -4830,39 +4839,39 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>299</v>
+        <v>60</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>367</v>
+      <c r="A81" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
-        <v>60</v>
+      <c r="A82" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="5" t="s">
-        <v>61</v>
+      <c r="A83" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="5" t="s">
-        <v>411</v>
+      <c r="A84" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>179</v>
@@ -4870,7 +4879,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>180</v>
@@ -4878,63 +4887,63 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>266</v>
+        <v>351</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>267</v>
+      <c r="A87" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
-        <v>351</v>
+      <c r="A88" s="5" t="s">
+        <v>288</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
-        <v>236</v>
+      <c r="A89" s="3" t="s">
+        <v>200</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="5" t="s">
-        <v>288</v>
+      <c r="A90" s="2" t="s">
+        <v>391</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
-        <v>200</v>
+      <c r="A91" s="2" t="s">
+        <v>394</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
-        <v>391</v>
+      <c r="A92" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
-        <v>394</v>
+      <c r="A93" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>188</v>
@@ -4942,7 +4951,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>62</v>
+        <v>201</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>189</v>
@@ -4950,7 +4959,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>63</v>
+        <v>202</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>190</v>
@@ -4958,7 +4967,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>191</v>
@@ -4966,7 +4975,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>202</v>
+        <v>64</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>192</v>
@@ -4974,7 +4983,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>203</v>
+        <v>462</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>193</v>
@@ -4982,1009 +4991,1004 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>64</v>
+        <v>204</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>194</v>
       </c>
     </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="3" t="s">
-        <v>462</v>
+      <c r="A102" s="2" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>204</v>
+        <v>66</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>65</v>
+        <v>407</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
-        <v>237</v>
+      <c r="A105" s="3" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
-        <v>395</v>
+      <c r="A106" s="5" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="3" t="s">
-        <v>66</v>
+      <c r="A107" s="5" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="3" t="s">
-        <v>407</v>
+      <c r="A108" s="5" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="3" t="s">
-        <v>408</v>
+      <c r="A109" s="2" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="5" t="s">
-        <v>412</v>
+      <c r="A110" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="5" t="s">
-        <v>413</v>
+      <c r="A111" s="2" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="5" t="s">
-        <v>414</v>
+      <c r="A112" s="2" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="3" t="s">
-        <v>67</v>
+      <c r="A114" s="2" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="2" t="s">
-        <v>356</v>
+      <c r="A117" s="3" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>357</v>
+        <v>386</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="2" t="s">
-        <v>358</v>
+      <c r="A119" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="2" t="s">
-        <v>359</v>
+      <c r="A120" s="3" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>368</v>
+        <v>15</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="2" t="s">
-        <v>386</v>
+      <c r="A122" s="3" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="3" t="s">
-        <v>14</v>
+      <c r="A123" s="2" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>415</v>
+        <v>68</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>205</v>
+        <v>303</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="2" t="s">
-        <v>423</v>
+      <c r="A127" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>68</v>
+        <v>238</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="3" t="s">
-        <v>251</v>
+      <c r="A129" s="2" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>303</v>
+        <v>268</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>69</v>
+        <v>418</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="2" t="s">
-        <v>329</v>
+      <c r="A133" s="3" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>268</v>
+        <v>417</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="3" t="s">
-        <v>418</v>
+      <c r="A135" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="3" t="s">
-        <v>206</v>
+      <c r="A136" s="2" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="3" t="s">
-        <v>416</v>
+      <c r="A137" s="2" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>417</v>
+        <v>207</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="2" t="s">
-        <v>330</v>
+      <c r="A139" s="3" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="2" t="s">
-        <v>331</v>
+      <c r="A140" s="3" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>332</v>
+        <v>396</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="3" t="s">
-        <v>207</v>
+      <c r="A142" s="2" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="3" t="s">
-        <v>360</v>
+      <c r="A143" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>373</v>
+        <v>403</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>396</v>
+        <v>334</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="2" t="s">
-        <v>208</v>
+      <c r="A148" s="3" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" s="2" t="s">
-        <v>397</v>
+      <c r="A149" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="2" t="s">
-        <v>333</v>
+      <c r="A151" s="3" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>403</v>
+        <v>70</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="2" t="s">
-        <v>334</v>
+      <c r="A153" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="3" t="s">
-        <v>365</v>
+      <c r="A154" s="2" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" s="3" t="s">
-        <v>21</v>
+      <c r="A155" s="2" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>293</v>
+        <v>72</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>281</v>
+        <v>209</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="3" t="s">
-        <v>71</v>
+      <c r="A159" s="2" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" s="3" t="s">
-        <v>72</v>
+      <c r="A163" s="2" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="3" t="s">
-        <v>209</v>
+      <c r="A164" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" s="3" t="s">
-        <v>73</v>
+      <c r="A166" s="2" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" s="2" t="s">
-        <v>337</v>
+      <c r="A167" s="3" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="2" t="s">
-        <v>338</v>
+      <c r="A168" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="2" t="s">
-        <v>340</v>
+      <c r="A170" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="2" t="s">
-        <v>341</v>
+      <c r="A171" s="3" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="2" t="s">
-        <v>342</v>
+      <c r="A172" s="3" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="2" t="s">
-        <v>343</v>
+      <c r="A173" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="2" t="s">
-        <v>344</v>
+      <c r="A174" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>210</v>
+        <v>76</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>211</v>
+        <v>361</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="2" t="s">
-        <v>345</v>
+      <c r="A177" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>212</v>
+        <v>31</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>292</v>
+        <v>29</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>419</v>
+        <v>30</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>75</v>
+        <v>426</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>361</v>
+        <v>301</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>28</v>
+        <v>291</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>426</v>
+        <v>82</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>301</v>
+        <v>10</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" s="3" t="s">
-        <v>291</v>
+      <c r="A193" s="5" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" s="3" t="s">
-        <v>78</v>
+      <c r="A194" s="2" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>79</v>
+        <v>213</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>9</v>
+        <v>306</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="5" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A202" s="2" t="s">
-        <v>249</v>
+      <c r="A202" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>213</v>
+        <v>300</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>83</v>
+        <v>290</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
-        <v>25</v>
+        <v>214</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>26</v>
+        <v>215</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>306</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" s="5" t="s">
-        <v>425</v>
+        <v>399</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>300</v>
+        <v>22</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>290</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>214</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>215</v>
+        <v>84</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>5</v>
+        <v>384</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A216" s="3" t="s">
-        <v>6</v>
+      <c r="A216" s="2" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A217" s="5" t="s">
-        <v>399</v>
+      <c r="A217" s="3" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A218" s="3" t="s">
-        <v>23</v>
+      <c r="A218" s="2" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A219" s="3" t="s">
-        <v>22</v>
+      <c r="A219" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A220" s="3" t="s">
-        <v>3</v>
+      <c r="A220" s="2" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
-        <v>4</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A223" s="3" t="s">
-        <v>84</v>
+      <c r="A223" s="2" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
-        <v>384</v>
+        <v>217</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A225" s="2" t="s">
-        <v>346</v>
+      <c r="A225" s="3" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
-        <v>85</v>
+        <v>363</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A227" s="2" t="s">
-        <v>240</v>
+      <c r="A227" s="3" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A228" s="2" t="s">
-        <v>241</v>
+      <c r="A228" s="3" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A229" s="2" t="s">
-        <v>325</v>
+      <c r="A229" s="3" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
-        <v>86</v>
+        <v>248</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
-        <v>216</v>
+        <v>87</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A232" s="2" t="s">
-        <v>324</v>
+      <c r="A232" s="3" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A233" s="3" t="s">
-        <v>217</v>
+      <c r="A233" s="2" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
-        <v>372</v>
+        <v>302</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
-        <v>371</v>
+        <v>88</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
-        <v>421</v>
+        <v>218</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A239" s="3" t="s">
-        <v>248</v>
+      <c r="A239" s="2" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A240" s="3" t="s">
-        <v>87</v>
+      <c r="A240" s="2" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A241" s="3" t="s">
-        <v>245</v>
+      <c r="A241" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A243" s="3" t="s">
-        <v>370</v>
+      <c r="A243" s="2" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A244" s="3" t="s">
-        <v>369</v>
+      <c r="A244" s="2" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A245" s="3" t="s">
-        <v>302</v>
+      <c r="A245" s="2" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A246" s="3" t="s">
-        <v>88</v>
+      <c r="A246" s="2" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A247" s="3" t="s">
-        <v>218</v>
+      <c r="A247" s="2" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A249" s="2" t="s">
-        <v>310</v>
+      <c r="A249" s="3" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A253" s="2" t="s">
-        <v>316</v>
+      <c r="A253" s="3" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A254" s="2" t="s">
-        <v>317</v>
+      <c r="A254" s="3" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A255" s="2" t="s">
-        <v>318</v>
+      <c r="A255" s="3" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>219</v>
+        <v>398</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A258" s="2" t="s">
-        <v>320</v>
+      <c r="A258" s="3" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A259" s="2" t="s">
-        <v>321</v>
+      <c r="A259" s="3" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A260" s="2" t="s">
-        <v>322</v>
+      <c r="A260" s="3" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A261" s="3" t="s">
-        <v>231</v>
+      <c r="A261" s="2" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A262" s="3" t="s">
-        <v>366</v>
+      <c r="A262" s="2" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
-        <v>287</v>
+        <v>323</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>326</v>
+        <v>295</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
-        <v>398</v>
+        <v>271</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
-        <v>221</v>
+        <v>272</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
-        <v>404</v>
+        <v>223</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A270" s="2" t="s">
-        <v>296</v>
+      <c r="A270" s="3" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A271" s="3" t="s">
-        <v>323</v>
+      <c r="A271" s="2" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A272" s="2" t="s">
-        <v>295</v>
+      <c r="A272" s="3" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273" s="3" t="s">
-        <v>271</v>
+        <v>224</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
-        <v>272</v>
+        <v>226</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
-        <v>223</v>
+        <v>375</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A277" s="2" t="s">
-        <v>297</v>
+      <c r="A277" s="3" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A279" s="2" t="s">
-        <v>298</v>
+      <c r="A279" s="5" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A280" s="3" t="s">
-        <v>89</v>
+      <c r="A280" s="2" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
-        <v>224</v>
+        <v>406</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A282" s="3" t="s">
-        <v>225</v>
+      <c r="A282" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284" s="3" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A285" s="3" t="s">
-        <v>226</v>
+      <c r="A285" s="2" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
-        <v>375</v>
+        <v>95</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
-        <v>374</v>
+        <v>282</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
-        <v>269</v>
+        <v>230</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A289" s="5" t="s">
-        <v>227</v>
+      <c r="A289" s="3" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A290" s="2" t="s">
-        <v>312</v>
+      <c r="A290" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291" s="3" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
-        <v>406</v>
+        <v>92</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>243</v>
+        <v>347</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
-        <v>229</v>
+        <v>93</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A295" s="3" t="s">
-        <v>90</v>
+      <c r="A295" s="5" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A296" s="2" t="s">
-        <v>313</v>
+      <c r="A296" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297" s="3" t="s">
-        <v>95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A300" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A301" s="3" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A303" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A304" s="3" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A306" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A307" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A308" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A311" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A312" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A313" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A314" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/Data/Variations.xlsx
+++ b/Data/Variations.xlsx
@@ -11,11 +11,12 @@
     <sheet name="Performance" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="577">
   <si>
     <t>flatten</t>
   </si>
@@ -185,9 +186,6 @@
     <t>cpow2</t>
   </si>
   <si>
-    <t>crackle (probably never)</t>
-  </si>
-  <si>
     <t>deltaA</t>
   </si>
   <si>
@@ -701,9 +699,6 @@
     <t>taurus</t>
   </si>
   <si>
-    <t>tess_v2</t>
-  </si>
-  <si>
     <t>truchet</t>
   </si>
   <si>
@@ -1175,9 +1170,6 @@
     <t>blur_heart</t>
   </si>
   <si>
-    <t>jacobi_elliptic</t>
-  </si>
-  <si>
     <t>loonie2</t>
   </si>
   <si>
@@ -1187,12 +1179,6 @@
     <t>csin (need C++ 11)</t>
   </si>
   <si>
-    <t>erf (need C++ 11)</t>
-  </si>
-  <si>
-    <t>gamma (need C++ 11)</t>
-  </si>
-  <si>
     <t>loonie3</t>
   </si>
   <si>
@@ -1277,9 +1263,6 @@
     <t>pie3D</t>
   </si>
   <si>
-    <t>pRose</t>
-  </si>
-  <si>
     <t>shredlin</t>
   </si>
   <si>
@@ -1718,9 +1701,6 @@
     <t>jac_sn (JWildfire)</t>
   </si>
   <si>
-    <t>smartcrop</t>
-  </si>
-  <si>
     <t>hexes</t>
   </si>
   <si>
@@ -1736,7 +1716,37 @@
     <t>crackle</t>
   </si>
   <si>
-    <t>smartshape</t>
+    <t>smartshape (no source)</t>
+  </si>
+  <si>
+    <t>tess_v2 (no source)</t>
+  </si>
+  <si>
+    <t>erf</t>
+  </si>
+  <si>
+    <t>xerf</t>
+  </si>
+  <si>
+    <t>jac_dn</t>
+  </si>
+  <si>
+    <t>pRose3D</t>
+  </si>
+  <si>
+    <t>pressure_wave</t>
+  </si>
+  <si>
+    <t>splits3D</t>
+  </si>
+  <si>
+    <t>jac_cn</t>
+  </si>
+  <si>
+    <t>jac_sn</t>
+  </si>
+  <si>
+    <t>gamma</t>
   </si>
 </sst>
 </file>
@@ -3693,11 +3703,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="40138752"/>
-        <c:axId val="108909632"/>
+        <c:axId val="121435648"/>
+        <c:axId val="108255424"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="40138752"/>
+        <c:axId val="121435648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3706,7 +3716,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="108909632"/>
+        <c:crossAx val="108255424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3714,7 +3724,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="108909632"/>
+        <c:axId val="108255424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3725,7 +3735,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="40138752"/>
+        <c:crossAx val="121435648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4068,7 +4078,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I298"/>
+  <dimension ref="A1:I312"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
@@ -4082,16 +4092,16 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" t="s">
@@ -4103,115 +4113,115 @@
         <v>47</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>284</v>
+        <v>568</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>285</v>
+        <v>559</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>352</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>289</v>
+        <v>560</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>353</v>
+        <v>563</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>568</v>
+        <v>101</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>387</v>
+        <v>571</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>392</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -4222,24 +4232,24 @@
         <v>40</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>41</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>569</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -4250,10 +4260,10 @@
         <v>42</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>571</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -4264,10 +4274,10 @@
         <v>43</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -4278,10 +4288,10 @@
         <v>44</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>567</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -4292,10 +4302,10 @@
         <v>45</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>420</v>
+        <v>109</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -4303,1698 +4313,1747 @@
         <v>2</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G18" s="2" t="s">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="E24" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="E30" s="4" t="s">
+      <c r="E32" s="4" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E34" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>235</v>
+      <c r="A37" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>377</v>
+      <c r="A39" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>54</v>
+        <v>374</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>379</v>
+        <v>54</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="E45" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>197</v>
+        <v>565</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>94</v>
+        <v>196</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>143</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="E48" s="4"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>381</v>
+        <v>93</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>380</v>
+        <v>245</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>389</v>
+      <c r="A51" s="3" t="s">
+        <v>379</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>349</v>
+      <c r="A53" s="2" t="s">
+        <v>386</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>16</v>
+        <v>346</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>383</v>
+        <v>347</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>198</v>
+        <v>381</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>350</v>
+        <v>56</v>
       </c>
       <c r="E58" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E59" s="4" t="s">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>199</v>
+        <v>258</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>12</v>
+        <v>259</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>262</v>
+        <v>198</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>390</v>
+      <c r="A69" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>264</v>
+        <v>568</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>382</v>
+        <v>261</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>58</v>
+        <v>380</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>59</v>
+        <v>263</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>424</v>
+        <v>57</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>299</v>
+        <v>418</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>367</v>
+        <v>20</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="E83" s="4" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E81" s="4" t="s">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="E84" s="4" t="s">
         <v>176</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>351</v>
+        <v>264</v>
       </c>
       <c r="E86" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E89" s="4" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E87" s="4" t="s">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="E90" s="4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="E88" s="4" t="s">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E91" s="4" t="s">
         <v>183</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>62</v>
+        <v>576</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="s">
-        <v>63</v>
+      <c r="A93" s="2" t="s">
+        <v>389</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>201</v>
+        <v>61</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>202</v>
+        <v>62</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>64</v>
+        <v>201</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>462</v>
+        <v>202</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>204</v>
+        <v>63</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>65</v>
+        <v>456</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
-        <v>237</v>
-      </c>
+      <c r="A101" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E101" s="4"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
-        <v>395</v>
-      </c>
+      <c r="A102" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E102" s="4"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="A103" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="E103" s="4"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>407</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="E104" s="4"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>408</v>
+        <v>203</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="5" t="s">
-        <v>412</v>
+      <c r="A106" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="5" t="s">
-        <v>413</v>
+      <c r="A107" s="2" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="5" t="s">
-        <v>414</v>
+      <c r="A108" s="2" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="2" t="s">
-        <v>328</v>
+      <c r="A109" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>67</v>
+        <v>402</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="2" t="s">
-        <v>354</v>
+      <c r="A111" s="3" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
-        <v>355</v>
+      <c r="A112" s="5" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
-        <v>356</v>
+      <c r="A113" s="5" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="2" t="s">
-        <v>357</v>
+      <c r="A114" s="5" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>358</v>
+        <v>326</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
-        <v>359</v>
+      <c r="A116" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="3" t="s">
-        <v>368</v>
+      <c r="A117" s="2" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>386</v>
+        <v>353</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="s">
-        <v>14</v>
+      <c r="A119" s="2" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="s">
-        <v>415</v>
+      <c r="A120" s="2" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="3" t="s">
-        <v>15</v>
+      <c r="A121" s="2" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="3" t="s">
-        <v>205</v>
+      <c r="A122" s="2" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="2" t="s">
-        <v>423</v>
+      <c r="A123" s="3" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="3" t="s">
-        <v>68</v>
+      <c r="A124" s="5" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="3" t="s">
-        <v>251</v>
+      <c r="A125" s="5" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="3" t="s">
-        <v>303</v>
+      <c r="A126" s="5" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>238</v>
+        <v>410</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="2" t="s">
-        <v>329</v>
+      <c r="A129" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>268</v>
+        <v>204</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="3" t="s">
-        <v>418</v>
+      <c r="A131" s="2" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>206</v>
+        <v>67</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>416</v>
+        <v>249</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>417</v>
+        <v>301</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="2" t="s">
-        <v>330</v>
+      <c r="A135" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="2" t="s">
-        <v>331</v>
+      <c r="A136" s="3" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>207</v>
+        <v>266</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>360</v>
+        <v>413</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>373</v>
+        <v>205</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="2" t="s">
-        <v>396</v>
+      <c r="A141" s="3" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="2" t="s">
-        <v>208</v>
+      <c r="A142" s="3" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>397</v>
+        <v>328</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="3" t="s">
-        <v>232</v>
+      <c r="A144" s="2" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>403</v>
+        <v>206</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="2" t="s">
-        <v>334</v>
+      <c r="A147" s="3" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>21</v>
+        <v>358</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>293</v>
+        <v>371</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="3" t="s">
-        <v>281</v>
+      <c r="A151" s="2" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="3" t="s">
-        <v>70</v>
+      <c r="A152" s="2" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="3" t="s">
-        <v>71</v>
+      <c r="A153" s="2" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="2" t="s">
-        <v>335</v>
+      <c r="A154" s="3" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>72</v>
+        <v>398</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="3" t="s">
-        <v>209</v>
+      <c r="A157" s="2" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>73</v>
+        <v>363</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="2" t="s">
-        <v>337</v>
+      <c r="A159" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" s="2" t="s">
-        <v>338</v>
+      <c r="A160" s="3" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" s="2" t="s">
-        <v>339</v>
+      <c r="A161" s="3" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" s="2" t="s">
-        <v>340</v>
+      <c r="A162" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" s="2" t="s">
-        <v>341</v>
+      <c r="A163" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" s="2" t="s">
-        <v>343</v>
+      <c r="A165" s="3" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>210</v>
+        <v>71</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="2" t="s">
-        <v>345</v>
+      <c r="A169" s="3" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="3" t="s">
-        <v>292</v>
+      <c r="A171" s="2" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="3" t="s">
-        <v>419</v>
+      <c r="A172" s="2" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="3" t="s">
-        <v>74</v>
+      <c r="A173" s="2" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="3" t="s">
-        <v>75</v>
+      <c r="A174" s="2" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" s="3" t="s">
-        <v>76</v>
+      <c r="A175" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" s="3" t="s">
-        <v>361</v>
+      <c r="A176" s="2" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="3" t="s">
-        <v>28</v>
+      <c r="A177" s="2" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" s="3" t="s">
-        <v>31</v>
+      <c r="A178" s="2" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>29</v>
+        <v>209</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>30</v>
+        <v>210</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" s="3" t="s">
-        <v>77</v>
+      <c r="A181" s="2" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>426</v>
+        <v>211</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>32</v>
+        <v>290</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>301</v>
+        <v>414</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>291</v>
+        <v>73</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>80</v>
+        <v>359</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" s="5" t="s">
-        <v>400</v>
+      <c r="A193" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" s="2" t="s">
-        <v>249</v>
+      <c r="A194" s="3" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>213</v>
+        <v>32</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>83</v>
+        <v>299</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
-        <v>25</v>
+        <v>289</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>306</v>
+        <v>78</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A201" s="5" t="s">
-        <v>425</v>
+      <c r="A201" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>300</v>
+        <v>9</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>290</v>
+        <v>10</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A205" s="3" t="s">
-        <v>214</v>
+      <c r="A205" s="5" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>215</v>
+        <v>247</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>5</v>
+        <v>212</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A209" s="5" t="s">
-        <v>399</v>
+      <c r="A209" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>22</v>
+        <v>304</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A213" s="3" t="s">
-        <v>4</v>
+      <c r="A213" s="5" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>384</v>
+        <v>298</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A216" s="2" t="s">
-        <v>346</v>
+      <c r="A216" s="3" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
-        <v>85</v>
+        <v>213</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A218" s="2" t="s">
-        <v>240</v>
+      <c r="A218" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A219" s="2" t="s">
-        <v>241</v>
+      <c r="A219" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A220" s="2" t="s">
-        <v>325</v>
+      <c r="A220" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A221" s="3" t="s">
-        <v>86</v>
+      <c r="A221" s="5" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
-        <v>216</v>
+        <v>23</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A223" s="2" t="s">
-        <v>324</v>
+      <c r="A223" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
-        <v>217</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
-        <v>362</v>
+        <v>4</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
-        <v>363</v>
+        <v>83</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A228" s="3" t="s">
-        <v>371</v>
+      <c r="A228" s="2" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
-        <v>421</v>
+        <v>84</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A230" s="3" t="s">
-        <v>248</v>
+      <c r="A230" s="2" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A231" s="3" t="s">
-        <v>87</v>
+      <c r="A231" s="2" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A232" s="3" t="s">
-        <v>245</v>
+      <c r="A232" s="2" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A233" s="2" t="s">
-        <v>307</v>
+      <c r="A233" s="3" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
-        <v>370</v>
+        <v>215</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A235" s="3" t="s">
-        <v>369</v>
+      <c r="A235" s="2" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
-        <v>302</v>
+        <v>216</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
-        <v>88</v>
+        <v>360</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
-        <v>218</v>
+        <v>361</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A239" s="2" t="s">
-        <v>309</v>
+      <c r="A239" s="3" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A240" s="2" t="s">
-        <v>310</v>
+      <c r="A240" s="3" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A241" s="2" t="s">
-        <v>308</v>
+      <c r="A241" s="3" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A242" s="2" t="s">
-        <v>314</v>
+      <c r="A242" s="3" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A243" s="2" t="s">
-        <v>573</v>
+      <c r="A243" s="3" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A244" s="2" t="s">
-        <v>315</v>
+      <c r="A244" s="3" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A246" s="2" t="s">
-        <v>317</v>
+      <c r="A246" s="3" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A247" s="2" t="s">
-        <v>318</v>
+      <c r="A247" s="3" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A248" s="2" t="s">
-        <v>319</v>
+      <c r="A248" s="3" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
-        <v>219</v>
+        <v>87</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A250" s="2" t="s">
-        <v>320</v>
+      <c r="A250" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A253" s="3" t="s">
-        <v>231</v>
+      <c r="A253" s="2" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A254" s="3" t="s">
-        <v>366</v>
+      <c r="A254" s="2" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A255" s="3" t="s">
-        <v>287</v>
+      <c r="A255" s="2" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A257" s="3" t="s">
-        <v>398</v>
+      <c r="A257" s="2" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A258" s="3" t="s">
-        <v>220</v>
+      <c r="A258" s="2" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A259" s="3" t="s">
-        <v>221</v>
+      <c r="A259" s="2" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A260" s="3" t="s">
-        <v>404</v>
+      <c r="A260" s="2" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A261" s="2" t="s">
-        <v>311</v>
+      <c r="A261" s="3" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A263" s="3" t="s">
-        <v>323</v>
+      <c r="A263" s="2" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
-        <v>271</v>
+        <v>229</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
-        <v>222</v>
+        <v>364</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A268" s="3" t="s">
-        <v>223</v>
+      <c r="A268" s="2" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A269" s="2" t="s">
-        <v>297</v>
+      <c r="A269" s="3" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A271" s="2" t="s">
-        <v>298</v>
+      <c r="A271" s="3" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
-        <v>89</v>
+        <v>399</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A273" s="3" t="s">
-        <v>224</v>
+      <c r="A273" s="2" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A274" s="3" t="s">
-        <v>225</v>
+      <c r="A274" s="2" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
-        <v>226</v>
+        <v>321</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A276" s="3" t="s">
-        <v>375</v>
+      <c r="A276" s="2" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277" s="3" t="s">
-        <v>374</v>
+        <v>269</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A279" s="5" t="s">
-        <v>227</v>
+      <c r="A279" s="3" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A280" s="2" t="s">
-        <v>312</v>
+      <c r="A280" s="3" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A281" s="3" t="s">
-        <v>406</v>
+      <c r="A281" s="2" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A282" s="2" t="s">
-        <v>243</v>
+      <c r="A282" s="3" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A283" s="3" t="s">
-        <v>229</v>
+      <c r="A283" s="2" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A285" s="2" t="s">
-        <v>313</v>
+      <c r="A285" s="3" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
-        <v>95</v>
+        <v>224</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A287" s="3" t="s">
-        <v>282</v>
+      <c r="A287" s="5" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
-        <v>91</v>
+        <v>372</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
-        <v>405</v>
+        <v>267</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A292" s="3" t="s">
-        <v>92</v>
+      <c r="A292" s="5" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>347</v>
+        <v>310</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A294" s="3" t="s">
-        <v>93</v>
+      <c r="A294" s="2" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A295" s="5" t="s">
-        <v>1</v>
+      <c r="A295" s="3" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A296" s="3" t="s">
-        <v>11</v>
+      <c r="A296" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297" s="3" t="s">
-        <v>7</v>
+        <v>227</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A299" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305" s="3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A312" s="3" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:A313">
-    <sortCondition ref="A313"/>
+  <sortState ref="G2:G15">
+    <sortCondition ref="G2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6012,7 +6071,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B1">
         <v>0</v>
@@ -6020,7 +6079,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6036,7 +6095,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6044,7 +6103,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6052,7 +6111,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6068,7 +6127,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -6076,7 +6135,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -6084,7 +6143,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -6092,7 +6151,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -6100,7 +6159,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -6116,7 +6175,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="B14" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6124,7 +6183,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B15" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6132,7 +6191,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B16" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6148,7 +6207,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B18" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6156,7 +6215,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B19" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6164,7 +6223,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B20" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6172,7 +6231,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B21" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6180,7 +6239,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B22" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6188,7 +6247,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="B23" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6196,7 +6255,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B24" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6204,7 +6263,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B25" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6212,7 +6271,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B26" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6220,7 +6279,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B27" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6228,7 +6287,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B28" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6236,7 +6295,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="B29" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6244,7 +6303,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B30" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6252,7 +6311,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B31" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6260,7 +6319,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="B32" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6268,7 +6327,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B33" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6276,7 +6335,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B34" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6292,7 +6351,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B36" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6308,7 +6367,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="B38" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6316,7 +6375,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B39" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6324,7 +6383,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B40" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6332,7 +6391,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B41" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6340,7 +6399,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B42" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6356,7 +6415,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B44" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6364,7 +6423,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B45" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6372,7 +6431,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B46" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6380,7 +6439,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B47" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6388,7 +6447,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B48" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6396,7 +6455,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B49" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6404,7 +6463,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B50" s="6">
         <v>3.1891599999999998E-5</v>
@@ -6420,7 +6479,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B52" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6428,7 +6487,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="B53" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6436,7 +6495,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B54" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6444,7 +6503,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B55" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6452,7 +6511,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B56" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6460,7 +6519,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B57" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6468,7 +6527,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B58" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6476,7 +6535,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B59" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6484,7 +6543,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B60" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6500,7 +6559,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B62" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6508,7 +6567,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B63" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6516,7 +6575,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B64" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6532,7 +6591,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B66" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6548,7 +6607,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B68" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6556,7 +6615,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B69" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6572,7 +6631,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B71" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6580,7 +6639,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B72" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6588,7 +6647,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B73" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6596,7 +6655,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B74" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6604,7 +6663,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="B75" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6612,7 +6671,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B76" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6620,7 +6679,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B77" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6628,7 +6687,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B78" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6636,7 +6695,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B79" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6644,7 +6703,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B80" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6652,7 +6711,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B81" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6660,7 +6719,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B82" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6668,7 +6727,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B83" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6676,7 +6735,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B84" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6684,7 +6743,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="B85" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6692,7 +6751,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="B86" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6700,7 +6759,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B87" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6708,7 +6767,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B88" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6716,7 +6775,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B89" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6724,7 +6783,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B90" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6732,7 +6791,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B91" s="6">
         <v>6.3783100000000003E-5</v>
@@ -6740,7 +6799,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B92" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6748,7 +6807,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B93" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6764,7 +6823,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B95" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6780,7 +6839,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B97" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6788,7 +6847,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="B98" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6796,7 +6855,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B99" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6804,7 +6863,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B100" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6812,7 +6871,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="B101" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6820,7 +6879,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B102" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6828,7 +6887,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="B103" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6836,7 +6895,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B104" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6844,7 +6903,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="B105" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6852,7 +6911,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B106" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6860,7 +6919,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B107" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6868,7 +6927,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B108" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6876,7 +6935,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="B109" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6884,7 +6943,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B110" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6892,7 +6951,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B111" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6900,7 +6959,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B112" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6908,7 +6967,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B113" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6916,7 +6975,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B114" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6924,7 +6983,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B115" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6932,7 +6991,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B116" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6940,7 +6999,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B117" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6948,7 +7007,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B118" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6956,7 +7015,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="B119" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6964,7 +7023,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B120" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6972,7 +7031,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="B121" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6980,7 +7039,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B122" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6988,7 +7047,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B123" s="6">
         <v>9.5674700000000001E-5</v>
@@ -6996,7 +7055,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B124" s="6">
         <v>9.5674700000000001E-5</v>
@@ -7004,7 +7063,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="B125" s="6">
         <v>9.5674700000000001E-5</v>
@@ -7012,7 +7071,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="B126" s="6">
         <v>9.5674700000000001E-5</v>
@@ -7020,7 +7079,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B127" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7036,7 +7095,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B129" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7044,7 +7103,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B130" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7052,7 +7111,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B131" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7060,7 +7119,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B132" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7068,7 +7127,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B133" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7076,7 +7135,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="B134" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7084,7 +7143,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B135" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7092,7 +7151,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B136" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7100,7 +7159,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="B137" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7108,7 +7167,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B138" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7116,7 +7175,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B139" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7124,7 +7183,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B140" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7156,7 +7215,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B144" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7164,7 +7223,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B145" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7172,7 +7231,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="B146" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7180,7 +7239,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="B147" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7188,7 +7247,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B148" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7196,7 +7255,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B149" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7204,7 +7263,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B150" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7212,7 +7271,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="B151" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7220,7 +7279,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B152" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7228,7 +7287,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B153" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7236,7 +7295,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B154" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7244,7 +7303,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B155" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7252,7 +7311,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B156" s="6">
         <v>1.2756599999999999E-4</v>
@@ -7260,7 +7319,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="B157" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7268,7 +7327,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B158" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7284,7 +7343,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B160" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7292,7 +7351,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B161" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7300,7 +7359,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B162" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7308,7 +7367,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B163" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7316,7 +7375,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B164" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7324,7 +7383,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B165" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7332,7 +7391,7 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B166" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7340,7 +7399,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B167" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7348,7 +7407,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="B168" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7356,7 +7415,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="B169" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7364,7 +7423,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="B170" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7372,7 +7431,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B171" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7380,7 +7439,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B172" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7388,7 +7447,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B173" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7396,7 +7455,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="B174" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7412,7 +7471,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B176" s="6">
         <v>1.5945799999999999E-4</v>
@@ -7428,7 +7487,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="B178" s="6">
         <v>1.91349E-4</v>
@@ -7436,7 +7495,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B179" s="6">
         <v>1.91349E-4</v>
@@ -7444,7 +7503,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="B180" s="6">
         <v>1.91349E-4</v>
@@ -7452,7 +7511,7 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B181" s="6">
         <v>1.91349E-4</v>
@@ -7460,7 +7519,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B182" s="6">
         <v>1.91349E-4</v>
@@ -7468,7 +7527,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B183" s="6">
         <v>1.91349E-4</v>
@@ -7476,7 +7535,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B184" s="6">
         <v>1.91349E-4</v>
@@ -7484,7 +7543,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B185" s="6">
         <v>1.91349E-4</v>
@@ -7492,7 +7551,7 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B186" s="6">
         <v>1.91349E-4</v>
@@ -7500,7 +7559,7 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="B187" s="6">
         <v>1.91349E-4</v>
@@ -7508,7 +7567,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="B188" s="6">
         <v>1.91349E-4</v>
@@ -7516,7 +7575,7 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="B189" s="6">
         <v>1.91349E-4</v>
@@ -7524,7 +7583,7 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B190" s="6">
         <v>1.91349E-4</v>
@@ -7532,7 +7591,7 @@
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B191" s="6">
         <v>1.91349E-4</v>
@@ -7540,7 +7599,7 @@
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B192" s="6">
         <v>1.91349E-4</v>
@@ -7548,7 +7607,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B193" s="6">
         <v>1.91349E-4</v>
@@ -7556,7 +7615,7 @@
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B194" s="6">
         <v>1.91349E-4</v>
@@ -7564,7 +7623,7 @@
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B195" s="6">
         <v>1.91349E-4</v>
@@ -7572,7 +7631,7 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B196" s="6">
         <v>1.91349E-4</v>
@@ -7580,7 +7639,7 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="B197" s="6">
         <v>1.91349E-4</v>
@@ -7588,7 +7647,7 @@
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B198" s="6">
         <v>1.91349E-4</v>
@@ -7596,7 +7655,7 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B199" s="6">
         <v>1.91349E-4</v>
@@ -7604,7 +7663,7 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B200" s="6">
         <v>2.23241E-4</v>
@@ -7612,7 +7671,7 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B201" s="6">
         <v>2.23241E-4</v>
@@ -7628,7 +7687,7 @@
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B203" s="6">
         <v>2.23241E-4</v>
@@ -7636,7 +7695,7 @@
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B204" s="6">
         <v>2.23241E-4</v>
@@ -7644,7 +7703,7 @@
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B205" s="6">
         <v>2.23241E-4</v>
@@ -7652,7 +7711,7 @@
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B206" s="6">
         <v>2.23241E-4</v>
@@ -7660,7 +7719,7 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B207" s="6">
         <v>2.23241E-4</v>
@@ -7676,7 +7735,7 @@
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B209" s="6">
         <v>2.23241E-4</v>
@@ -7684,7 +7743,7 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B210" s="6">
         <v>2.23241E-4</v>
@@ -7692,7 +7751,7 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B211" s="6">
         <v>2.23241E-4</v>
@@ -7700,7 +7759,7 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B212" s="6">
         <v>2.23241E-4</v>
@@ -7708,7 +7767,7 @@
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B213" s="6">
         <v>2.23241E-4</v>
@@ -7716,7 +7775,7 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B214" s="6">
         <v>2.23241E-4</v>
@@ -7724,7 +7783,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B215" s="6">
         <v>2.23241E-4</v>
@@ -7732,7 +7791,7 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B216" s="6">
         <v>2.23241E-4</v>
@@ -7740,7 +7799,7 @@
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B217" s="6">
         <v>2.23241E-4</v>
@@ -7748,7 +7807,7 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B218" s="6">
         <v>2.23241E-4</v>
@@ -7756,7 +7815,7 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B219" s="6">
         <v>2.23241E-4</v>
@@ -7764,7 +7823,7 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B220" s="6">
         <v>2.55133E-4</v>
@@ -7772,7 +7831,7 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B221" s="6">
         <v>2.55133E-4</v>
@@ -7780,7 +7839,7 @@
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B222" s="6">
         <v>2.55133E-4</v>
@@ -7788,7 +7847,7 @@
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B223" s="6">
         <v>2.55133E-4</v>
@@ -7796,7 +7855,7 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B224" s="6">
         <v>2.55133E-4</v>
@@ -7812,7 +7871,7 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B226" s="6">
         <v>2.55133E-4</v>
@@ -7820,7 +7879,7 @@
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B227" s="6">
         <v>2.55133E-4</v>
@@ -7828,7 +7887,7 @@
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="B228" s="6">
         <v>2.55133E-4</v>
@@ -7836,7 +7895,7 @@
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="B229" s="6">
         <v>2.55133E-4</v>
@@ -7844,7 +7903,7 @@
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B230" s="6">
         <v>2.55133E-4</v>
@@ -7852,7 +7911,7 @@
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="B231" s="6">
         <v>2.55133E-4</v>
@@ -7860,7 +7919,7 @@
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B232" s="6">
         <v>2.55133E-4</v>
@@ -7868,7 +7927,7 @@
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="B233" s="6">
         <v>2.55133E-4</v>
@@ -7876,7 +7935,7 @@
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B234" s="6">
         <v>2.55133E-4</v>
@@ -7892,7 +7951,7 @@
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B236" s="6">
         <v>2.55133E-4</v>
@@ -7900,7 +7959,7 @@
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B237" s="6">
         <v>2.55133E-4</v>
@@ -7908,7 +7967,7 @@
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="B238" s="6">
         <v>2.55133E-4</v>
@@ -7916,7 +7975,7 @@
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B239" s="6">
         <v>2.55133E-4</v>
@@ -7924,7 +7983,7 @@
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B240" s="6">
         <v>2.55133E-4</v>
@@ -7932,7 +7991,7 @@
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B241" s="6">
         <v>2.55133E-4</v>
@@ -7940,7 +7999,7 @@
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B242" s="6">
         <v>2.55133E-4</v>
@@ -7948,7 +8007,7 @@
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="B243" s="6">
         <v>2.8702399999999998E-4</v>
@@ -7956,7 +8015,7 @@
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B244" s="6">
         <v>2.8702399999999998E-4</v>
@@ -7964,7 +8023,7 @@
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B245" s="6">
         <v>2.8702399999999998E-4</v>
@@ -7972,7 +8031,7 @@
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B246" s="6">
         <v>2.8702399999999998E-4</v>
@@ -7980,7 +8039,7 @@
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B247" s="6">
         <v>2.8702399999999998E-4</v>
@@ -7988,7 +8047,7 @@
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="B248" s="6">
         <v>2.8702399999999998E-4</v>
@@ -7996,7 +8055,7 @@
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B249" s="6">
         <v>2.8702399999999998E-4</v>
@@ -8004,7 +8063,7 @@
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B250" s="6">
         <v>2.8702399999999998E-4</v>
@@ -8012,7 +8071,7 @@
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B251" s="6">
         <v>2.8702399999999998E-4</v>
@@ -8020,7 +8079,7 @@
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="B252" s="6">
         <v>2.8702399999999998E-4</v>
@@ -8028,7 +8087,7 @@
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B253" s="6">
         <v>2.8702399999999998E-4</v>
@@ -8036,7 +8095,7 @@
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B254" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8044,7 +8103,7 @@
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B255" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8052,7 +8111,7 @@
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B256" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8060,7 +8119,7 @@
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="B257" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8068,7 +8127,7 @@
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B258" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8076,7 +8135,7 @@
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="B259" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8084,7 +8143,7 @@
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B260" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8092,7 +8151,7 @@
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="B261" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8100,7 +8159,7 @@
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B262" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8108,7 +8167,7 @@
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B263" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8116,7 +8175,7 @@
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="B264" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8124,7 +8183,7 @@
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B265" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8132,7 +8191,7 @@
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B266" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8140,7 +8199,7 @@
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B267" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8156,7 +8215,7 @@
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B269" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8164,7 +8223,7 @@
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B270" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8172,7 +8231,7 @@
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="B271" s="6">
         <v>3.1891599999999998E-4</v>
@@ -8180,7 +8239,7 @@
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B272" s="6">
         <v>3.5080700000000002E-4</v>
@@ -8188,7 +8247,7 @@
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B273" s="6">
         <v>3.5080700000000002E-4</v>
@@ -8196,7 +8255,7 @@
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B274" s="6">
         <v>3.5080700000000002E-4</v>
@@ -8204,7 +8263,7 @@
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="B275" s="6">
         <v>3.5080700000000002E-4</v>
@@ -8212,7 +8271,7 @@
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B276" s="6">
         <v>3.5080700000000002E-4</v>
@@ -8220,7 +8279,7 @@
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B277" s="6">
         <v>3.5080700000000002E-4</v>
@@ -8228,7 +8287,7 @@
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B278" s="6">
         <v>3.8269900000000002E-4</v>
@@ -8236,7 +8295,7 @@
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B279" s="6">
         <v>3.8269900000000002E-4</v>
@@ -8244,7 +8303,7 @@
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B280" s="6">
         <v>3.8269900000000002E-4</v>
@@ -8252,7 +8311,7 @@
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="B281" s="6">
         <v>4.1459E-4</v>
@@ -8260,7 +8319,7 @@
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B282" s="6">
         <v>4.1459E-4</v>
@@ -8268,7 +8327,7 @@
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B283" s="6">
         <v>4.1459E-4</v>
@@ -8276,7 +8335,7 @@
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B284" s="6">
         <v>4.1459E-4</v>
@@ -8284,7 +8343,7 @@
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B285" s="6">
         <v>4.46482E-4</v>
@@ -8292,7 +8351,7 @@
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B286" s="6">
         <v>4.46482E-4</v>
@@ -8300,7 +8359,7 @@
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="B287" s="6">
         <v>4.78374E-4</v>
@@ -8308,7 +8367,7 @@
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B288" s="6">
         <v>4.78374E-4</v>
@@ -8316,7 +8375,7 @@
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B289" s="6">
         <v>4.78374E-4</v>
@@ -8324,7 +8383,7 @@
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B290" s="6">
         <v>4.78374E-4</v>
@@ -8332,7 +8391,7 @@
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="B291" s="6">
         <v>4.78374E-4</v>
@@ -8340,7 +8399,7 @@
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B292" s="6">
         <v>5.1026499999999998E-4</v>
@@ -8348,7 +8407,7 @@
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="B293" s="6">
         <v>5.4215700000000003E-4</v>
@@ -8356,7 +8415,7 @@
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B294" s="6">
         <v>5.4215700000000003E-4</v>
@@ -8364,7 +8423,7 @@
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="B295" s="6">
         <v>5.7404799999999996E-4</v>
@@ -8372,7 +8431,7 @@
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B296" s="6">
         <v>6.3783100000000005E-4</v>
@@ -8380,7 +8439,7 @@
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B297" s="6">
         <v>6.3783100000000005E-4</v>
@@ -8388,7 +8447,7 @@
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="B298" s="6">
         <v>7.0161500000000005E-4</v>
@@ -8396,7 +8455,7 @@
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="B299" s="6">
         <v>7.3350599999999998E-4</v>
@@ -8412,7 +8471,7 @@
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B301" s="6">
         <v>9.5674699999999998E-4</v>
